--- a/assets/ALMA_Weekly_Timetable.xlsx
+++ b/assets/ALMA_Weekly_Timetable.xlsx
@@ -2,24 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19 Oct" sheetId="1" r:id="Rab9094493bb042e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26 Oct" sheetId="2" r:id="Rae57cf075b5a4719"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Nov" sheetId="3" r:id="R82401d9e4ea54f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Nov" sheetId="4" r:id="Rbaaf91ed5006471f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16 Nov" sheetId="5" r:id="R6914c7f8d0be4f3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23 Nov" sheetId="6" r:id="Ra45fc21f551e4a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30 Nov" sheetId="7" r:id="R5980646e75b54cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Dec" sheetId="8" r:id="R6ff664a51b3e473f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 Dec" sheetId="9" r:id="Rfc84234ddb8e40e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Dec" sheetId="10" r:id="R175da3bb2348458b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28 Dec" sheetId="11" r:id="Rea4591c978564d76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Jan" sheetId="12" r:id="Rf9efb451f9324dc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Jan" sheetId="13" r:id="R00af5e3bd06e479d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18 Jan" sheetId="14" r:id="R4868fd6511e34058"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 Jan" sheetId="15" r:id="Ra052de0d4591462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Feb" sheetId="16" r:id="R4131f1027edd4e51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Feb" sheetId="17" r:id="Rb8c06d98546042b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15 Feb" sheetId="18" r:id="R854521c232684fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19 Oct" sheetId="1" r:id="R421bceab4d2740da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26 Oct" sheetId="2" r:id="Rf5a0ffe00e114ccc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Nov" sheetId="3" r:id="R3b456745a1704955"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Nov" sheetId="4" r:id="Rf508cab9cd584bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16 Nov" sheetId="5" r:id="Rd4c84fb64d3e4231"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23 Nov" sheetId="6" r:id="Rca2731b589ad4c67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30 Nov" sheetId="7" r:id="Rda315dc4e13f43c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Dec" sheetId="8" r:id="Ra5f52d8e07324dab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 Dec" sheetId="9" r:id="R660f9848f0654dcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Dec" sheetId="10" r:id="Rfc0c3d9e7f244566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28 Dec" sheetId="11" r:id="R606c3882e58b41ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Jan" sheetId="12" r:id="Re86e2d50bf12479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Jan" sheetId="13" r:id="R9e9668d269144409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18 Jan" sheetId="14" r:id="R2d2e89f8857d4345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 Jan" sheetId="15" r:id="R1040e0c138cc4d4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Feb" sheetId="16" r:id="Rea885303cf3549cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Feb" sheetId="17" r:id="R3ca630a548664993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15 Feb" sheetId="18" r:id="Rabd9832fbf744df8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,7 +30,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -77,6 +77,11 @@
     <x:font>
       <x:sz val="11"/>
       <x:color rgb="FF475569"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF64748B"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -479,7 +484,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="549">
+  <x:cellXfs count="553">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1614,6 +1619,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="75" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1838,13 +1855,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -2805,6 +2824,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -2834,13 +2856,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -3479,6 +3503,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -3508,13 +3535,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -3742,6 +3771,7 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="B5:F5"/>
+    <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3772,13 +3802,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -3841,8 +3873,8 @@
 20 Nov 2026 – 05 Feb 2027
 Seminar-/Besprechungsraum 181 (OSA-Keplerstr.)
 Prof. Dr. phil. Lea Frermann
-Specific dates only: 20 and 27 Nov 09:00–11:00; 08 and 29 Jan, 05
-Feb 09:00–12:00 (course description).</x:v>
+Specific dates only: 20 and 27 Nov 2026; 08 and 29 Jan, 05 Feb
+2027. All sessions 09:00–12:00 (ALMA appointment table).</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -4362,6 +4394,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -4391,13 +4426,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -5386,6 +5423,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -5415,13 +5455,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -6410,6 +6452,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -6439,13 +6484,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -6508,8 +6555,8 @@
 20 Nov 2026 – 05 Feb 2027
 Seminar-/Besprechungsraum 181 (OSA-Keplerstr.)
 Prof. Dr. phil. Lea Frermann
-Specific dates only: 20 and 27 Nov 09:00–11:00; 08 and 29 Jan, 05
-Feb 09:00–12:00 (course description).</x:v>
+Specific dates only: 20 and 27 Nov 2026; 08 and 29 Jan, 05 Feb
+2027. All sessions 09:00–12:00 (ALMA appointment table).</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -7471,6 +7518,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -7500,13 +7550,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -7569,8 +7621,8 @@
 20 Nov 2026 – 05 Feb 2027
 Seminar-/Besprechungsraum 181 (OSA-Keplerstr.)
 Prof. Dr. phil. Lea Frermann
-Specific dates only: 20 and 27 Nov 09:00–11:00; 08 and 29 Jan, 05
-Feb 09:00–12:00 (course description).</x:v>
+Specific dates only: 20 and 27 Nov 2026; 08 and 29 Jan, 05 Feb
+2027. All sessions 09:00–12:00 (ALMA appointment table).</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -8532,6 +8584,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -8561,13 +8616,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -8931,6 +8988,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -8960,13 +9020,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -9330,6 +9392,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -9359,13 +9424,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -10342,6 +10409,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -10371,13 +10441,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -11366,6 +11438,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -11395,13 +11470,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -12390,6 +12467,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -12419,13 +12499,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -12469,7 +12551,7 @@
       <x:c r="D5"/>
       <x:c r="E5"/>
       <x:c r="F5" s="526" t="str">
-        <x:v>09:00–11:00 | Advanced Seminar
+        <x:v>09:00–12:00 | Advanced Seminar
 Cross-disciplinary Perspectives on Narratives</x:v>
       </x:c>
     </x:row>
@@ -12488,8 +12570,8 @@
 20 Nov 2026 – 05 Feb 2027
 Seminar-/Besprechungsraum 181 (OSA-Keplerstr.)
 Prof. Dr. phil. Lea Frermann
-Specific dates only: 20 and 27 Nov 09:00–11:00; 08 and 29 Jan, 05
-Feb 09:00–12:00 (course description).</x:v>
+Specific dates only: 20 and 27 Nov 2026; 08 and 29 Jan, 05 Feb
+2027. All sessions 09:00–12:00 (ALMA appointment table).</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -13451,6 +13533,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -13480,13 +13565,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -13530,7 +13617,7 @@
       <x:c r="D5"/>
       <x:c r="E5"/>
       <x:c r="F5" s="526" t="str">
-        <x:v>09:00–11:00 | Advanced Seminar
+        <x:v>09:00–12:00 | Advanced Seminar
 Cross-disciplinary Perspectives on Narratives</x:v>
       </x:c>
     </x:row>
@@ -13549,8 +13636,8 @@
 20 Nov 2026 – 05 Feb 2027
 Seminar-/Besprechungsraum 181 (OSA-Keplerstr.)
 Prof. Dr. phil. Lea Frermann
-Specific dates only: 20 and 27 Nov 09:00–11:00; 08 and 29 Jan, 05
-Feb 09:00–12:00 (course description).</x:v>
+Specific dates only: 20 and 27 Nov 2026; 08 and 29 Jan, 05 Feb
+2027. All sessions 09:00–12:00 (ALMA appointment table).</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -14512,6 +14599,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -14541,13 +14631,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -15536,6 +15628,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -15565,13 +15660,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -16560,6 +16657,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -16589,13 +16689,15 @@
       <x:c r="E1" s="227"/>
       <x:c r="F1" s="227"/>
     </x:row>
-    <x:row r="2" ht="13.550000190734863" customHeight="1">
-      <x:c r="A2" s="7"/>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="552" t="str">
+        <x:v>Updated 18 Oct 2026, 13:46 CEST</x:v>
+      </x:c>
+      <x:c r="B2" s="552"/>
+      <x:c r="C2" s="552"/>
+      <x:c r="D2" s="552"/>
+      <x:c r="E2" s="552"/>
+      <x:c r="F2" s="552"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="228" t="str">
@@ -17584,6 +17686,9 @@
     <x:row r="149" ht="15" customHeight="1"/>
     <x:row r="150" ht="15" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>